--- a/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:45</t>
+          <t>2026-09-03 00:52:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:47</t>
+          <t>2026-09-03 00:53:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:48</t>
+          <t>2026-09-03 00:53:02</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:33:49</t>
+          <t>2026-09-03 00:53:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 00:52:59</t>
+          <t>2026-09-03 01:13:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:00</t>
+          <t>2026-09-03 01:13:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:02</t>
+          <t>2026-09-03 01:13:16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:03</t>
+          <t>2026-09-03 01:13:17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:03</t>
+          <t>2026-09-03 01:13:17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:03</t>
+          <t>2026-09-03 01:13:17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:03</t>
+          <t>2026-09-03 01:13:17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 00:53:03</t>
+          <t>2026-09-03 01:13:17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.51%588,000</t>
+          <t>13.37%588,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.51%</t>
+          <t>13.37%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.7%361.5</t>
+          <t>-3.04%350.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>-3.04%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>361.5</v>
+        <v>350.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.11%1,215,000</t>
+          <t>4.19%1,215,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.11%56,000</t>
+          <t>4.16%167,036</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.16%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>56000</v>
+        <v>167036</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.49%102.5</t>
+          <t>+0.98%103.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>+0.98%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>102.5</v>
+        <v>103.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.64%3,832,000</t>
+          <t>3.74%3,832,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.74%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.1%137.5</t>
+          <t>+0.36%138</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>137.5</v>
+        <v>138</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.62%2,828,000</t>
+          <t>3.71%2,828,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.71%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.87%138,000</t>
+          <t>2.81%138,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.81%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2383台光電子材料</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5445</v>
+        <v>4340</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.76%52,000</t>
+          <t>2.73%67,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>52000</v>
+        <v>67000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4275</v>
+        <v>5290</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.72%67,000</t>
+          <t>2.70%52,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.70%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>67000</v>
+        <v>52000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.50%435,000</t>
+          <t>2.44%435,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3310</v>
+        <v>3300</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.44%76,000</t>
+          <t>2.40%76,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.22%72.6</t>
+          <t>-2.2%71</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.22%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>72.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.92%2300</t>
+          <t>-4.35%2200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.92%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.38%108,000</t>
+          <t>2.37%108,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>973</v>
+        <v>923</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.30%252,000</t>
+          <t>2.34%252,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2170</v>
+        <v>2100</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.29%105,000</t>
+          <t>2.17%105,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:13</t>
+          <t>2026-09-03 21:25:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.75%4200</t>
+          <t>0%4050</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.13%53,000</t>
+          <t>2.12%53,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.67%692</t>
+          <t>-2.6%674</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.67%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.10%313,000</t>
+          <t>2.06%313,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.06%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.93%540</t>
+          <t>+1.31%50.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>540</v>
+        <v>50.2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.05%383,000</t>
+          <t>1.97%4,181,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>383000</v>
+        <v>4181000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2027大成不銹鋼工業</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.5%49.55</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>49.55</v>
+        <v>511</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.96%4,181,000</t>
+          <t>1.97%383,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>4181000</v>
+        <v>383000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.84%105,000</t>
+          <t>1.73%105,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.73%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>+3.45%1350</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+3.45%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1305</v>
+        <v>1350</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.70%138,000</t>
+          <t>1.72%138,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.49%20.45</t>
+          <t>+0.49%20.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20.45</v>
+        <v>20.55</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.68%8,783,000</t>
+          <t>1.71%8,783,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.47%234.5</t>
+          <t>+1.92%239</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>234.5</v>
+        <v>239</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.63%726,000</t>
+          <t>1.62%726,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.72%967</t>
+          <t>-4.14%927</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.72%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.63%174,000</t>
+          <t>1.60%174,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.95%251</t>
+          <t>-1.39%247.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.52%629,000</t>
+          <t>1.50%629,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3105穩懋半導體</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.57%469.5</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>469.5</v>
+        <v>5615</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.51%326,000</t>
+          <t>1.48%27,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>326000</v>
+        <v>27000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>3491昇達科技</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-2.77%1405</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5770</v>
+        <v>1405</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.50%27,000</t>
+          <t>1.47%107,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>27000</v>
+        <v>107000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3491昇達科技</t>
+          <t>3105穩懋半導體</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.36%1445</t>
+          <t>-4.9%446.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.36%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1445</v>
+        <v>446.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.49%107,000</t>
+          <t>1.46%326,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>107000</v>
+        <v>326000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1200</v>
+        <v>1080</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.44%125,000</t>
+          <t>1.43%125,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.55%1340</t>
+          <t>-2.99%1300</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1340</v>
+        <v>1300</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.42%110,000</t>
+          <t>1.40%110,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:15</t>
+          <t>2026-09-03 21:25:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1265</v>
+        <v>1185</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.25%113,000</t>
+          <t>1.36%113,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.52%76.6</t>
+          <t>-1.39%1770</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>76.59999999999999</v>
+        <v>1770</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.19%1,657,000</t>
+          <t>1.27%74,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1657000</v>
+        <v>74000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-1.31%75.6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>7810</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.14%16,000</t>
+          <t>1.21%1,657,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>16000</v>
+        <v>1657000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+9.79%1795</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+9.79%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1795</v>
+        <v>7150</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.14%74,000</t>
+          <t>1.19%16,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>74000</v>
+        <v>16000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1301台灣塑膠工業</t>
+          <t>3081聯亞光電工業</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.47%66.8</t>
+          <t>-8.1%3120</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>66.8</v>
+        <v>3120</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.01%1,577,000</t>
+          <t>1.00%31,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1577000</v>
+        <v>31000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>1301台灣塑膠工業</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-1.65%65.7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>126</v>
+        <v>65.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.00%804,000</t>
+          <t>1.00%1,577,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>804000</v>
+        <v>1577000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3081聯亞光電工業</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.88%3395</t>
+          <t>+2.8%5870</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+2.8%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3395</v>
+        <v>5870</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.00%31,000</t>
+          <t>0.98%18,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>31000</v>
+        <v>18000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.73%5710</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.73%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5710</v>
+        <v>125</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.99%18,000</t>
+          <t>0.97%804,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>18000</v>
+        <v>804000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0%518</t>
+          <t>-7.82%477.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>518</v>
+        <v>477.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.94%193,000</t>
+          <t>0.95%193,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.01%13865</t>
+          <t>-2.99%13450</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.01%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>13865</v>
+        <v>13450</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.54%182.5</t>
+          <t>+3.56%189</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>182.5</v>
+        <v>189</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.89%517,000</t>
+          <t>0.90%517,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1975</v>
+        <v>2015</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.82%43,000</t>
+          <t>0.81%43,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.7%179</t>
+          <t>-5.59%169</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>-5.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.40%243,000</t>
+          <t>0.41%243,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-3.02%2405</t>
+          <t>-1.66%2365</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>-1.66%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2405</v>
+        <v>2365</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>-8.48%464</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-8.48%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>507</v>
+        <v>464</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.23%46,000</t>
+          <t>0.22%46,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:16</t>
+          <t>2026-09-03 21:25:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2881富邦金融控股</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-4.08%1175</t>
+          <t>+2.44%147</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>+2.44%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1175</v>
+        <v>147</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.22%19,000</t>
+          <t>0.21%154,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>19000</v>
+        <v>154000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:17</t>
+          <t>2026-09-03 21:25:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2881富邦金融控股</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.03%143.5</t>
+          <t>-6.38%1100</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.03%</t>
+          <t>-6.38%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>143.5</v>
+        <v>1100</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.21%154,000</t>
+          <t>0.21%19,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,11 +3276,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>154000</v>
+        <v>19000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:17</t>
+          <t>2026-09-03 21:25:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.15%66.6</t>
+          <t>+1.35%67.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>66.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:17</t>
+          <t>2026-09-03 21:25:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.82%2065</t>
+          <t>-3.15%2000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2065</v>
+        <v>2000</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:17</t>
+          <t>2026-09-03 21:25:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-4.59%187</t>
+          <t>+1.87%190.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.59%</t>
+          <t>+1.87%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>187</v>
+        <v>190.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:13:17</t>
+          <t>2026-09-03 21:25:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.09%847</t>
+          <t>-8.5%775</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.09%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>847</v>
+        <v>775</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:37</t>
+          <t>2026-09-03 21:40:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:39</t>
+          <t>2026-09-03 21:40:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:40</t>
+          <t>2026-09-03 21:40:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:41</t>
+          <t>2026-09-03 21:40:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:41</t>
+          <t>2026-09-03 21:40:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:41</t>
+          <t>2026-09-03 21:40:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:41</t>
+          <t>2026-09-03 21:40:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:25:41</t>
+          <t>2026-09-03 21:40:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:18</t>
+          <t>2026-09-03 22:32:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:20</t>
+          <t>2026-09-03 22:32:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:21</t>
+          <t>2026-09-03 22:32:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:22</t>
+          <t>2026-09-03 22:32:27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:22</t>
+          <t>2026-09-03 22:32:27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:22</t>
+          <t>2026-09-03 22:32:27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:22</t>
+          <t>2026-09-03 22:32:27</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:40:22</t>
+          <t>2026-09-03 22:32:27</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:23</t>
+          <t>2026-09-03 22:44:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:25</t>
+          <t>2026-09-03 22:44:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:26</t>
+          <t>2026-09-03 22:44:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:27</t>
+          <t>2026-09-03 22:44:53</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:27</t>
+          <t>2026-09-03 22:44:53</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:27</t>
+          <t>2026-09-03 22:44:53</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:27</t>
+          <t>2026-09-03 22:44:53</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:32:27</t>
+          <t>2026-09-03 22:44:53</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:49</t>
+          <t>2026-09-03 23:00:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:50</t>
+          <t>2026-09-03 23:00:42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:52</t>
+          <t>2026-09-03 23:00:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:53</t>
+          <t>2026-09-03 23:00:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
